--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_2_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_2_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319650.2816502029</v>
+        <v>322259.061560525</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547406</v>
+        <v>2989156.853416515</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20349704.61069185</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813076.283068547</v>
+        <v>4821032.195206849</v>
       </c>
     </row>
     <row r="11">
@@ -901,13 +901,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.6263639150735023</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -974,19 +974,19 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1056,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1132,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1183,13 +1183,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="9">
@@ -1211,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1247,16 +1247,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -1320,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1369,16 +1369,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>10.61706312961832</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9608114308426619</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -1402,16 +1402,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1484,16 +1484,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1515,34 +1515,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1597,28 +1597,28 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H14" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1676,16 +1676,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1767,16 +1767,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0.2968606583479628</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -1843,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>12.71311064538747</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>22.02246762618611</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2037,16 +2037,16 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2113,28 +2113,28 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>94.41048699370604</v>
       </c>
       <c r="X20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2159,19 +2159,19 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>54.22805157515521</v>
+        <v>83.03189205754171</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2195,25 +2195,25 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2368,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="24">
@@ -2387,16 +2387,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>137.0424786983366</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>193.4635395755014</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>220.1862512213238</v>
+        <v>220.8837963815378</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2596,16 +2596,16 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2672,22 +2672,22 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>56.91690033700354</v>
       </c>
       <c r="W27" t="n">
-        <v>218.6652504806746</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -2748,7 +2748,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>47.02492433367362</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>230.1769504358686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2833,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="30">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>97.39304467772196</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>99.18221148611876</v>
       </c>
     </row>
     <row r="31">
@@ -3025,13 +3025,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3061,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>179.7283339446665</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="33">
@@ -3101,19 +3101,19 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>68.21377427677575</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3152,16 +3152,16 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>198.5990147965225</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3237,10 +3237,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3253,19 +3253,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3319,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="36">
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>107.7584848665749</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3380,28 +3380,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>204.9483021474179</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3471,10 +3471,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3493,16 +3493,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="F38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3541,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>173.4119418445973</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>179.7283339446665</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3623,22 +3623,22 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>199.4303350649351</v>
       </c>
       <c r="V39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>204.2072713051783</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3648,13 +3648,13 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>177.6197007854552</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3739,16 +3739,16 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="G41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3793,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="Y41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3860,22 +3860,22 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>195.7256592341942</v>
       </c>
       <c r="U42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
-        <v>187.6104</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>39.82778746869526</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>130.4655268502615</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F8" t="n">
-        <v>92.93786803496215</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G8" t="n">
-        <v>66.67524177233588</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H8" t="n">
-        <v>40.41261550970962</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I8" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L8" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M8" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N8" t="n">
-        <v>52.52000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W8" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y8" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L9" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M9" t="n">
-        <v>52.52000000000001</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N9" t="n">
-        <v>78.26000000000001</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H10" t="n">
-        <v>51.19778581548745</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I10" t="n">
-        <v>24.93515955286119</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J10" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K10" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O10" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q10" t="n">
-        <v>77.46041207811371</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y10" t="n">
-        <v>51.19778581548745</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F11" t="n">
-        <v>15.12050584389412</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="G11" t="n">
-        <v>15.12050584389412</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="H11" t="n">
-        <v>15.12050584389412</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="I11" t="n">
-        <v>14.14998924708335</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>52.52000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M11" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O11" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>67.64575836914665</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S11" t="n">
-        <v>41.38313210652039</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L12" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M12" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N12" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="O12" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>103.72303834074</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="C13" t="n">
-        <v>103.72303834074</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="D13" t="n">
-        <v>103.72303834074</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E13" t="n">
-        <v>103.72303834074</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="F13" t="n">
-        <v>103.72303834074</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G13" t="n">
-        <v>103.72303834074</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="H13" t="n">
-        <v>77.46041207811371</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="I13" t="n">
-        <v>51.19778581548745</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y13" t="n">
-        <v>103.72303834074</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="F14" t="n">
-        <v>77.73737373737373</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="G14" t="n">
-        <v>51.47474747474747</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="H14" t="n">
-        <v>40.41261550970962</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="I14" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L14" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M14" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N14" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O14" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C15" t="n">
-        <v>77.73737373737373</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D15" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E15" t="n">
-        <v>25.2121212121212</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M15" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="O15" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>99.15847409556821</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="G17" t="n">
-        <v>70.87564581273992</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H17" t="n">
-        <v>42.59281752991163</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I17" t="n">
-        <v>14.30998924708335</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>29.96</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>29.96</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="L18" t="n">
-        <v>57.68</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M18" t="n">
-        <v>85.40000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>55.43434343434343</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>55.43434343434343</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="U18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24.48491679412739</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="T19" t="n">
-        <v>81.05057335978395</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="U19" t="n">
-        <v>52.76774507695567</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V19" t="n">
-        <v>52.76774507695567</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W19" t="n">
-        <v>52.76774507695567</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X19" t="n">
-        <v>52.76774507695567</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>52.76774507695567</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C20" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D20" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E20" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S20" t="n">
-        <v>953.9083846317729</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T20" t="n">
-        <v>953.9083846317729</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="U20" t="n">
-        <v>710.4740411974295</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="V20" t="n">
-        <v>710.4740411974295</v>
+        <v>114.6452713866835</v>
       </c>
       <c r="W20" t="n">
-        <v>710.4740411974295</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X20" t="n">
-        <v>467.0396977630861</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y20" t="n">
-        <v>467.0396977630861</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>417.2095324773084</v>
+        <v>277.6047704292607</v>
       </c>
       <c r="C21" t="n">
-        <v>417.2095324773084</v>
+        <v>103.1517411481337</v>
       </c>
       <c r="D21" t="n">
-        <v>417.2095324773084</v>
+        <v>103.1517411481337</v>
       </c>
       <c r="E21" t="n">
-        <v>417.2095324773084</v>
+        <v>103.1517411481337</v>
       </c>
       <c r="F21" t="n">
-        <v>362.4337228054344</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G21" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>851.7806659261865</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>660.6438759116518</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>660.6438759116518</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>660.6438759116518</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W21" t="n">
-        <v>417.2095324773084</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X21" t="n">
-        <v>417.2095324773084</v>
+        <v>277.6047704292607</v>
       </c>
       <c r="Y21" t="n">
-        <v>417.2095324773084</v>
+        <v>277.6047704292607</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>233.6969696969697</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="C23" t="n">
-        <v>233.6969696969697</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="D23" t="n">
-        <v>233.6969696969697</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="W23" t="n">
-        <v>720.5656565656566</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="X23" t="n">
-        <v>477.1313131313132</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="Y23" t="n">
-        <v>233.6969696969697</v>
+        <v>231.8830517671884</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>352.9704842865825</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="C24" t="n">
-        <v>178.5174550054555</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="D24" t="n">
-        <v>178.5174550054555</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>234.7819638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>768.5822832570693</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>768.5822832570693</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V24" t="n">
-        <v>768.5822832570693</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W24" t="n">
-        <v>768.5822832570693</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X24" t="n">
-        <v>560.7307830515365</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y24" t="n">
-        <v>352.9704842865825</v>
+        <v>304.9965798960495</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
       <c r="C26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
       <c r="D26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
       <c r="E26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
       <c r="F26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
       <c r="G26" t="n">
-        <v>241.690354769014</v>
+        <v>467.067986854209</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T26" t="n">
-        <v>728.5590416377008</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U26" t="n">
-        <v>485.1246982033574</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V26" t="n">
-        <v>485.1246982033574</v>
+        <v>710.516763498309</v>
       </c>
       <c r="W26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
       <c r="X26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
       <c r="Y26" t="n">
-        <v>485.1246982033574</v>
+        <v>467.067986854209</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>193.733029281127</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M27" t="n">
-        <v>383.2275600578374</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N27" t="n">
-        <v>473.3719638733197</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>790.5826554506689</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V27" t="n">
-        <v>790.5826554506689</v>
+        <v>678.3417187247995</v>
       </c>
       <c r="W27" t="n">
-        <v>569.708665066149</v>
+        <v>434.8929420806995</v>
       </c>
       <c r="X27" t="n">
-        <v>569.708665066149</v>
+        <v>227.0414418751666</v>
       </c>
       <c r="Y27" t="n">
-        <v>361.9483663011951</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>66.7799235693673</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R28" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="S28" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="T28" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="U28" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="V28" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>251.781970137241</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="C29" t="n">
-        <v>251.781970137241</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D29" t="n">
-        <v>251.781970137241</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>719.4169572236606</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T29" t="n">
-        <v>738.6506570059279</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U29" t="n">
-        <v>495.2163135715845</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V29" t="n">
-        <v>495.2163135715845</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W29" t="n">
-        <v>495.2163135715845</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X29" t="n">
-        <v>495.2163135715845</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="Y29" t="n">
-        <v>251.781970137241</v>
+        <v>426.43660147347</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>194.4871619339127</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L30" t="n">
-        <v>65.58652238664914</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M30" t="n">
-        <v>304.1765223866491</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="U30" t="n">
-        <v>735.7763817363891</v>
+        <v>542.8367666556771</v>
       </c>
       <c r="V30" t="n">
-        <v>500.6242735046464</v>
+        <v>325.2670720263557</v>
       </c>
       <c r="W30" t="n">
-        <v>500.6242735046464</v>
+        <v>325.2670720263557</v>
       </c>
       <c r="X30" t="n">
-        <v>500.6242735046464</v>
+        <v>117.4155718208228</v>
       </c>
       <c r="Y30" t="n">
-        <v>292.8639747396925</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="C32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="E32" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M32" t="n">
-        <v>504.9505276501126</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N32" t="n">
-        <v>710.8050498573519</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O32" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S32" t="n">
-        <v>860</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="T32" t="n">
-        <v>860</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="U32" t="n">
-        <v>860</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="V32" t="n">
-        <v>860</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="W32" t="n">
-        <v>860</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="X32" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="Y32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.2</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="C33" t="n">
-        <v>17.2</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="D33" t="n">
-        <v>17.2</v>
+        <v>575.103493803018</v>
       </c>
       <c r="E33" t="n">
-        <v>17.2</v>
+        <v>415.8660387975625</v>
       </c>
       <c r="F33" t="n">
-        <v>17.2</v>
+        <v>269.3314808244475</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>130.6006554070629</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L33" t="n">
-        <v>142.5575600578374</v>
+        <v>221.8558176135191</v>
       </c>
       <c r="M33" t="n">
-        <v>355.4075600578374</v>
+        <v>435.095875319717</v>
       </c>
       <c r="N33" t="n">
-        <v>464.5065223866492</v>
+        <v>648.335933025915</v>
       </c>
       <c r="O33" t="n">
-        <v>677.3565223866492</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U33" t="n">
-        <v>659.3949345489672</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="V33" t="n">
-        <v>442.22321737725</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="W33" t="n">
-        <v>225.0515002055328</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="X33" t="n">
-        <v>17.2</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="Y33" t="n">
-        <v>17.2</v>
+        <v>644.0062961027915</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>415.5649502883385</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="C35" t="n">
-        <v>415.5649502883385</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D35" t="n">
-        <v>415.5649502883385</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M35" t="n">
-        <v>513.1408574955809</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N35" t="n">
-        <v>718.9953797028202</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X35" t="n">
-        <v>849.9083846317729</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="Y35" t="n">
-        <v>632.7366674600557</v>
+        <v>426.43660147347</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>126.0469544106817</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>17.2</v>
+        <v>152.4612591001897</v>
       </c>
       <c r="M36" t="n">
-        <v>230.05</v>
+        <v>365.7013168063877</v>
       </c>
       <c r="N36" t="n">
-        <v>442.9</v>
+        <v>578.9413745125856</v>
       </c>
       <c r="O36" t="n">
-        <v>655.75</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="P36" t="n">
-        <v>838.3934776133508</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T36" t="n">
-        <v>758.8304705528857</v>
+        <v>659.389396090879</v>
       </c>
       <c r="U36" t="n">
-        <v>758.8304705528857</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="V36" t="n">
-        <v>758.8304705528857</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="W36" t="n">
-        <v>541.6587533811685</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X36" t="n">
-        <v>333.8072531756357</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y36" t="n">
-        <v>126.0469544106817</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>246.4417064188005</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="C38" t="n">
-        <v>246.4417064188005</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D38" t="n">
-        <v>246.4417064188005</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E38" t="n">
-        <v>246.4417064188005</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F38" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G38" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H38" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M38" t="n">
-        <v>513.1408574955809</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>718.9953797028202</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S38" t="n">
-        <v>638.7770012113231</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T38" t="n">
-        <v>463.6134235905177</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U38" t="n">
-        <v>463.6134235905177</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="V38" t="n">
-        <v>463.6134235905177</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="W38" t="n">
-        <v>463.6134235905177</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="X38" t="n">
-        <v>463.6134235905177</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="Y38" t="n">
-        <v>246.4417064188005</v>
+        <v>669.9406037026066</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>38.80652238664919</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M39" t="n">
-        <v>251.6565223866492</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="N39" t="n">
-        <v>464.5065223866492</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="O39" t="n">
-        <v>677.3565223866492</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T39" t="n">
-        <v>657.813405358766</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U39" t="n">
-        <v>657.813405358766</v>
+        <v>660.1312078382391</v>
       </c>
       <c r="V39" t="n">
-        <v>440.6416881870488</v>
+        <v>442.5615132089176</v>
       </c>
       <c r="W39" t="n">
-        <v>223.4699710153316</v>
+        <v>224.9918185795962</v>
       </c>
       <c r="X39" t="n">
-        <v>223.4699710153316</v>
+        <v>224.9918185795962</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C40" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="D40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>626.7568694802578</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="C41" t="n">
-        <v>447.3430303030303</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="D41" t="n">
-        <v>447.3430303030303</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="E41" t="n">
-        <v>447.3430303030303</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="F41" t="n">
-        <v>232.1915151515151</v>
+        <v>422.536925949487</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>206.9568616895446</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>206.9568616895446</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>300.1647985849684</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>511.4548195661379</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="W41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="X41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="Y41" t="n">
-        <v>626.7568694802578</v>
+        <v>638.1169902094293</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L42" t="n">
-        <v>149.9954414866706</v>
+        <v>228.3639620705569</v>
       </c>
       <c r="M42" t="n">
-        <v>360.8654414866706</v>
+        <v>439.6539830517264</v>
       </c>
       <c r="N42" t="n">
-        <v>571.7354414866707</v>
+        <v>459.7635558748512</v>
       </c>
       <c r="O42" t="n">
-        <v>782.6054414866707</v>
+        <v>671.0535768560208</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>655.994368374226</v>
       </c>
       <c r="U42" t="n">
-        <v>636.8484848484849</v>
+        <v>655.994368374226</v>
       </c>
       <c r="V42" t="n">
-        <v>421.6969696969697</v>
+        <v>440.4143041142837</v>
       </c>
       <c r="W42" t="n">
-        <v>206.5454545454546</v>
+        <v>224.8342398543413</v>
       </c>
       <c r="X42" t="n">
-        <v>17.04</v>
+        <v>224.8342398543413</v>
       </c>
       <c r="Y42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>111.3761432274407</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>111.3761432274407</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>111.3761432274407</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>111.3761432274407</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>111.3761432274407</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>148.8233604548096</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
     </row>
     <row r="44">
@@ -8199,19 +8199,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L5" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M5" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N5" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O5" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P5" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q5" t="n">
         <v>212.3149906599047</v>
@@ -8275,10 +8275,10 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L6" t="n">
-        <v>138.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M6" t="n">
         <v>142.1340339220183</v>
@@ -8287,13 +8287,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P6" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8357,16 +8357,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L7" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M7" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N7" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O7" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P7" t="n">
         <v>135.0065633140411</v>
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>245.0393459944755</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L8" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M8" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L9" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M9" t="n">
-        <v>167.0835288715133</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N9" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>142.5962444444444</v>
+        <v>167.1813723584841</v>
       </c>
       <c r="P9" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>245.0393459944755</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M11" t="n">
-        <v>230.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,7 +8749,7 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>163.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -8761,13 +8761,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>167.5457393939394</v>
+        <v>167.1813723584841</v>
       </c>
       <c r="P12" t="n">
-        <v>159.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>245.0393459944755</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>256.0982114216868</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P14" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,7 +8986,7 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>163.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -8995,16 +8995,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>142.5962444444444</v>
+        <v>167.1813723584841</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,19 +9144,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>257.2149200959596</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
         <v>231.2329957552695</v>
@@ -9223,19 +9223,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>165.841438974359</v>
+        <v>164.3167157393088</v>
       </c>
       <c r="L18" t="n">
-        <v>166.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>170.1340339220183</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N18" t="n">
-        <v>158.2103989520202</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
         <v>133.9744074143302</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,13 +9466,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>244.7225752110828</v>
       </c>
       <c r="O21" t="n">
-        <v>255.9491071452661</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>133.9744074143302</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,19 +9697,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>231.1529892133072</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
@@ -9867,7 +9867,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O26" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
         <v>321.7987081714826</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>222.3966654323053</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>295.1552315763977</v>
       </c>
       <c r="Q27" t="n">
         <v>210.0772877358491</v>
@@ -10092,22 +10092,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M29" t="n">
-        <v>449.5135334928325</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N29" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O29" t="n">
-        <v>380.8001812627454</v>
+        <v>373.6931947635578</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7987081714826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>185.3286448168935</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>183.0115685892478</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>437.0731727773048</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,22 +10408,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>345.2455896777295</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N33" t="n">
-        <v>241.5426841326382</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
         <v>139.9817740860215</v>
@@ -10566,19 +10566,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
-        <v>281.9614083965644</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
         <v>321.7987081714826</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>148.5262779896823</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>161.806544173546</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,22 +10803,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>372.5271208127775</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10882,19 +10882,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>160.3791498673986</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>253.5692927615014</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
@@ -11046,10 +11046,10 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>338.5882684418997</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
-        <v>437.3469244119842</v>
+        <v>333.8446085143028</v>
       </c>
       <c r="O41" t="n">
         <v>380.8001812627454</v>
@@ -11122,22 +11122,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>272.8528055239859</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>151.6544119046715</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22759,13 +22759,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H5" t="n">
-        <v>339.4748021157671</v>
+        <v>338.8484382006936</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22786,13 +22786,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S5" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T5" t="n">
         <v>223.0958495641314</v>
@@ -22832,19 +22832,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>145.0692123933839</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22914,16 +22914,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.9909793584588</v>
+        <v>142.3706881638279</v>
       </c>
       <c r="H7" t="n">
-        <v>162.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I7" t="n">
-        <v>155.4504749272583</v>
+        <v>132.8841224430275</v>
       </c>
       <c r="J7" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K7" t="n">
         <v>22.26949182588285</v>
@@ -22978,7 +22978,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382.7338416634806</v>
+        <v>360.1674891792497</v>
       </c>
       <c r="C8" t="n">
         <v>365.2728917710076</v>
@@ -22990,19 +22990,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>395.924535096324</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23041,13 +23041,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X8" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="9">
@@ -23069,19 +23069,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809748</v>
+        <v>203.375029596744</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,16 +23151,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9909793584588</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H10" t="n">
-        <v>162.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23178,13 +23178,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.447248692439088</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23227,16 +23227,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>406.8760457417114</v>
+        <v>396.2589826120931</v>
       </c>
       <c r="G11" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H11" t="n">
-        <v>339.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I11" t="n">
-        <v>209.5150781395633</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23260,16 +23260,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
         <v>251.3456529078365</v>
@@ -23306,19 +23306,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>203.375029596744</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>179.8319801819373</v>
+        <v>154.2116889873065</v>
       </c>
       <c r="C13" t="n">
         <v>167.2468210986278</v>
       </c>
       <c r="D13" t="n">
-        <v>148.6154730182124</v>
+        <v>122.9951818235815</v>
       </c>
       <c r="E13" t="n">
         <v>146.4339626465692</v>
       </c>
       <c r="F13" t="n">
-        <v>145.4210480229312</v>
+        <v>122.8546955387004</v>
       </c>
       <c r="G13" t="n">
         <v>167.9909793584588</v>
       </c>
       <c r="H13" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23415,7 +23415,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.447248692439088</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
         <v>86.16204325169439</v>
@@ -23455,28 +23455,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
-        <v>365.2728917710076</v>
+        <v>339.6526005763767</v>
       </c>
       <c r="D14" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E14" t="n">
-        <v>381.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F14" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H14" t="n">
-        <v>328.5232914703797</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>184.4758895704059</v>
+        <v>187.9095370861751</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23534,16 +23534,16 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>146.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
-        <v>121.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
-        <v>131.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.1684123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
         <v>137.3435171632106</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S15" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>203.375029596744</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23701,19 +23701,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>394.162935096324</v>
+        <v>382.574751492425</v>
       </c>
       <c r="G17" t="n">
-        <v>387.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>311.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>182.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23780,10 +23780,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>117.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>112.6811171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
         <v>112.2354442364965</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>143.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>201.6400878316884</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23847,10 +23847,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>151.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C19" t="n">
-        <v>145.2243534724417</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D19" t="n">
         <v>148.6154730182124</v>
@@ -23895,16 +23895,16 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>177.2933913771695</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
-        <v>199.9455894282815</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>263.8702699959815</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
@@ -23947,7 +23947,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
-        <v>8.193788784950669</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -23971,28 +23971,28 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>254.830481723707</v>
       </c>
       <c r="X20" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
         <v>386.2379386560536</v>
@@ -24008,7 +24008,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -24017,19 +24017,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>90.84116081822866</v>
+        <v>62.03732033584217</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,25 +24053,25 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -24138,7 +24138,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U22" t="n">
         <v>286.3190293564909</v>
@@ -24153,7 +24153,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="23">
@@ -24172,7 +24172,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>169.6575700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
@@ -24184,7 +24184,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24217,7 +24217,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>221.2863534910952</v>
       </c>
       <c r="U23" t="n">
         <v>251.3456529078365</v>
@@ -24226,13 +24226,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X23" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="24">
@@ -24245,16 +24245,16 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>35.66602028997912</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>137.3435171632106</v>
@@ -24266,7 +24266,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24296,7 +24296,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>6.701189119320247</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -24305,7 +24305,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -24366,16 +24366,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
         <v>286.3190293564909</v>
@@ -24415,16 +24415,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>119.2885508944433</v>
+        <v>118.5910057342293</v>
       </c>
       <c r="I26" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24454,16 +24454,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W26" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X26" t="n">
         <v>369.731100678469</v>
@@ -24479,10 +24479,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
@@ -24530,22 +24530,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>175.8836868124217</v>
       </c>
       <c r="W27" t="n">
-        <v>33.02973268024496</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -24606,7 +24606,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>130.2684670434959</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
         <v>224.0165980369723</v>
@@ -24624,7 +24624,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
-        <v>225.7096553890372</v>
+        <v>178.6847310553635</v>
       </c>
       <c r="Y28" t="n">
         <v>218.5846533520948</v>
@@ -24637,16 +24637,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>167.3398439804523</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>175.5538586117964</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>151.7534196363932</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
         <v>406.8760457417114</v>
@@ -24691,10 +24691,10 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24703,10 +24703,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>154.3371029954408</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="30">
@@ -24716,10 +24716,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69.14013897214538</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24740,7 +24740,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -24773,19 +24773,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W30" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>106.5004842911856</v>
       </c>
     </row>
     <row r="31">
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.3976857667268</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="32">
@@ -24883,13 +24883,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>191.8760457417114</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24919,13 +24919,13 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>29.29173564157887</v>
       </c>
       <c r="T32" t="n">
         <v>223.0958495641314</v>
@@ -24940,10 +24940,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>180.3591006784691</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>171.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="33">
@@ -24959,19 +24959,19 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>79.231291287863</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25010,16 +25010,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>27.34236728445234</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V33" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
         <v>205.6826957773044</v>
@@ -25095,10 +25095,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X34" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
         <v>218.5846533520948</v>
@@ -25111,19 +25111,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>167.3398439804523</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>175.5538586117964</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>202.5490692868066</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
         <v>415.302737515135</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25177,10 +25177,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>154.3371029954408</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="36">
@@ -25193,7 +25193,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>64.95001412174084</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
@@ -25238,28 +25238,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>20.99307993355688</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -25329,10 +25329,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X37" t="n">
         <v>225.7096553890372</v>
@@ -25351,16 +25351,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D38" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>166.5363723892335</v>
       </c>
       <c r="F38" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
@@ -25372,7 +25372,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25399,10 +25399,10 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>49.68390771953406</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
         <v>251.3456529078365</v>
@@ -25414,10 +25414,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>190.0027667338026</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25481,22 +25481,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>26.51104701603975</v>
       </c>
       <c r="V39" t="n">
-        <v>17.80058714942527</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.475424472126093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25506,13 +25506,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>46.6450125965693</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C40" t="n">
         <v>167.2468210986278</v>
       </c>
       <c r="D40" t="n">
-        <v>148.6154730182124</v>
+        <v>15.42850543284433</v>
       </c>
       <c r="E40" t="n">
         <v>146.4339626465692</v>
@@ -25588,7 +25588,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>187.6531909855524</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25597,16 +25597,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>193.8760457417114</v>
+        <v>193.4517821243685</v>
       </c>
       <c r="G41" t="n">
-        <v>202.302737515135</v>
+        <v>201.8784738977921</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>22.49179817625028</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25651,10 +25651,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>369.731100678469</v>
+        <v>156.3068370611261</v>
       </c>
       <c r="Y41" t="n">
-        <v>173.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25718,22 +25718,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>4.439069460627451</v>
       </c>
       <c r="U42" t="n">
-        <v>12.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>19.80058714942527</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
-        <v>18.16258520347745</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25752,7 +25752,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E43" t="n">
-        <v>146.4339626465692</v>
+        <v>106.6061751778739</v>
       </c>
       <c r="F43" t="n">
         <v>145.4210480229312</v>
@@ -25767,7 +25767,7 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J43" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>22.26949182588285</v>
@@ -25785,7 +25785,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
         <v>86.16204325169439</v>
@@ -25809,7 +25809,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
-        <v>95.24412853877561</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
         <v>218.5846533520948</v>
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>327897.5868709115</v>
+        <v>350049.7958156171</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350365.0263125471</v>
+        <v>350049.7958156171</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350365.0263125471</v>
+        <v>350049.7958156169</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350365.0263125472</v>
+        <v>350049.7958156171</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352010.6902785869</v>
+        <v>351685.049566824</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506898.8173466545</v>
+        <v>506909.1411107076</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107078</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506898.8173466545</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506898.8173466544</v>
+        <v>488398.3911706115</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488113.7264674625</v>
+        <v>488398.3911706115</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488113.7264674625</v>
+        <v>488398.3911706117</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488113.7264674625</v>
+        <v>488398.3911706117</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486668.7194767555</v>
+        <v>486975.2514232371</v>
       </c>
     </row>
     <row r="16">
@@ -26264,46 +26264,46 @@
         <v>59129.07304229552</v>
       </c>
       <c r="C2" t="n">
+        <v>63121.07616893066</v>
+      </c>
+      <c r="D2" t="n">
+        <v>63121.07616893067</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63121.07616893067</v>
+      </c>
+      <c r="F2" t="n">
+        <v>63121.07616893066</v>
+      </c>
+      <c r="G2" t="n">
+        <v>63415.7618187435</v>
+      </c>
+      <c r="H2" t="n">
+        <v>91388.36989223283</v>
+      </c>
+      <c r="I2" t="n">
+        <v>91388.3698922328</v>
+      </c>
+      <c r="J2" t="n">
+        <v>91388.3698922328</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88052.58645764727</v>
+      </c>
+      <c r="L2" t="n">
+        <v>88052.58645764727</v>
+      </c>
+      <c r="M2" t="n">
+        <v>88052.58645764728</v>
+      </c>
+      <c r="N2" t="n">
+        <v>88052.58645764727</v>
+      </c>
+      <c r="O2" t="n">
+        <v>87796.12542771843</v>
+      </c>
+      <c r="P2" t="n">
         <v>59129.07304229552</v>
-      </c>
-      <c r="D2" t="n">
-        <v>63177.88319582794</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63177.88319582796</v>
-      </c>
-      <c r="F2" t="n">
-        <v>63177.88319582796</v>
-      </c>
-      <c r="G2" t="n">
-        <v>63474.44484862834</v>
-      </c>
-      <c r="H2" t="n">
-        <v>91386.50946835901</v>
-      </c>
-      <c r="I2" t="n">
-        <v>91386.50946835897</v>
-      </c>
-      <c r="J2" t="n">
-        <v>91386.50946835897</v>
-      </c>
-      <c r="K2" t="n">
-        <v>91386.50946835894</v>
-      </c>
-      <c r="L2" t="n">
-        <v>88001.28762835899</v>
-      </c>
-      <c r="M2" t="n">
-        <v>88001.28762835896</v>
-      </c>
-      <c r="N2" t="n">
-        <v>88001.28762835894</v>
-      </c>
-      <c r="O2" t="n">
-        <v>87740.88594835893</v>
-      </c>
-      <c r="P2" t="n">
-        <v>59129.07304229551</v>
       </c>
     </row>
     <row r="3">
@@ -26316,10 +26316,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>8277.165051769143</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="D4" t="n">
-        <v>11524.36744801407</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="E4" t="n">
-        <v>11524.36744801407</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="F4" t="n">
-        <v>11524.36744801407</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="G4" t="n">
-        <v>11581.0330020641</v>
+        <v>11299.21161664248</v>
       </c>
       <c r="H4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="I4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="J4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="K4" t="n">
-        <v>16914.33416026179</v>
+        <v>15899.57777605044</v>
       </c>
       <c r="L4" t="n">
-        <v>16267.50248349411</v>
+        <v>15899.57777605043</v>
       </c>
       <c r="M4" t="n">
-        <v>16267.50248349411</v>
+        <v>15899.57777605043</v>
       </c>
       <c r="N4" t="n">
-        <v>16267.50248349411</v>
+        <v>15899.57777605043</v>
       </c>
       <c r="O4" t="n">
-        <v>16217.74620066583</v>
+        <v>15851.6895168862</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
     </row>
     <row r="5">
@@ -26420,43 +26420,43 @@
         <v>33627.6</v>
       </c>
       <c r="C5" t="n">
-        <v>33627.6</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>15002.70297086521</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>8414.411632653479</v>
       </c>
       <c r="D6" t="n">
-        <v>8368.735747813873</v>
+        <v>16691.57668442264</v>
       </c>
       <c r="E6" t="n">
-        <v>50072.71574781388</v>
+        <v>50319.17668442264</v>
       </c>
       <c r="F6" t="n">
-        <v>50072.71574781388</v>
+        <v>50319.17668442262</v>
       </c>
       <c r="G6" t="n">
-        <v>49642.84184656424</v>
+        <v>49899.20210488044</v>
       </c>
       <c r="H6" t="n">
-        <v>2350.058308097225</v>
+        <v>2628.454590704194</v>
       </c>
       <c r="I6" t="n">
-        <v>59819.37530809718</v>
+        <v>60212.24173303586</v>
       </c>
       <c r="J6" t="n">
-        <v>59819.37530809718</v>
+        <v>60212.24173303584</v>
       </c>
       <c r="K6" t="n">
-        <v>59819.37530809715</v>
+        <v>59057.05362246872</v>
       </c>
       <c r="L6" t="n">
-        <v>58661.78514486487</v>
+        <v>59057.05362246872</v>
       </c>
       <c r="M6" t="n">
-        <v>58661.78514486484</v>
+        <v>59057.05362246874</v>
       </c>
       <c r="N6" t="n">
-        <v>58661.78514486483</v>
+        <v>59057.05362246872</v>
       </c>
       <c r="O6" t="n">
-        <v>58572.7397476931</v>
+        <v>58968.24068289778</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>48630.30297086521</v>
       </c>
     </row>
   </sheetData>
@@ -26730,43 +26730,43 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26898,7 +26898,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26925,7 +26925,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26934,7 +26934,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,13 +26944,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -26959,10 +26959,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -26971,22 +26971,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27188,10 +27188,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -34854,19 +34854,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -34930,10 +34930,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -34942,13 +34942,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35012,16 +35012,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -35088,22 +35088,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M9" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,22 +35325,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,7 +35404,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -35416,13 +35416,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>24.94949494949496</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,7 +35641,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -35650,16 +35650,16 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,19 +35799,19 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>26.86868686868687</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -35878,19 +35878,19 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="L18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N18" t="n">
-        <v>26.86868686868686</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,13 +36121,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="O21" t="n">
-        <v>113.3528627008217</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,19 +36352,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>99.8112771299739</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
@@ -36522,7 +36522,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O26" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
         <v>90.5657124162131</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>91.05495334897201</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>161.1808241620674</v>
       </c>
       <c r="Q27" t="n">
         <v>70.09551364982758</v>
@@ -36747,22 +36747,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
-        <v>219.1673002655598</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N29" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O29" t="n">
-        <v>150.7019698410586</v>
+        <v>143.5949833418711</v>
       </c>
       <c r="P29" t="n">
-        <v>90.5657124162131</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>46.77426503701933</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>40.87753466722953</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>206.726939550032</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,22 +37063,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>206.6912098978554</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N33" t="n">
-        <v>110.2009720493049</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37221,19 +37221,19 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
-        <v>51.86319697487763</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
         <v>90.5657124162131</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>9.971898209808174</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>21.82477008752445</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,22 +37458,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>142.4289093910907</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37537,19 +37537,19 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>21.82477008752444</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>110.973048317057</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
@@ -37701,10 +37701,10 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>108.242035214627</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
-        <v>207.9338608153932</v>
+        <v>104.4315449177119</v>
       </c>
       <c r="O41" t="n">
         <v>150.7019698410586</v>
@@ -37777,22 +37777,22 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>134.2984257441118</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>20.31269982133822</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
